--- a/Revision/01_需蔡老師補做資料表/table4_external_validation_full_with_ci.xlsx
+++ b/Revision/01_需蔡老師補做資料表/table4_external_validation_full_with_ci.xlsx
@@ -642,124 +642,124 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8867580061870668</v>
+        <v>0.8976695635440358</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004152817659835308</v>
+        <v>0.004220883846517569</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8785145089688412</v>
+        <v>0.8891750419529203</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8951421635869541</v>
+        <v>0.9057388034286502</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8283462033462033</v>
+        <v>0.8484555984555985</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003927199322504861</v>
+        <v>0.003975746084846248</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8208614864864865</v>
+        <v>0.8405727155727156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8356700450450451</v>
+        <v>0.8564993564993565</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8562874251497006</v>
+        <v>0.8552074513124471</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0104539793042737</v>
+        <v>0.009774808562368271</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8357290139296187</v>
+        <v>0.8362477357455836</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8783698388721047</v>
+        <v>0.8746781115879828</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4817518248175183</v>
+        <v>0.5670971364402021</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01191973882272997</v>
+        <v>0.0116235594567582</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4606822010106682</v>
+        <v>0.5446238068500843</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5047725996631106</v>
+        <v>0.5895564289724874</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4817518248175183</v>
+        <v>0.5670971364402021</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01191973882272997</v>
+        <v>0.0116235594567582</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4606822010106682</v>
+        <v>0.5446238068500843</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5047725996631106</v>
+        <v>0.5895564289724874</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9675310033821871</v>
+        <v>0.9614430665163473</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002616359253119222</v>
+        <v>0.00291766192878763</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9625704622322435</v>
+        <v>0.9555806087936866</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.97271702367531</v>
+        <v>0.9668602029312289</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8562874251497006</v>
+        <v>0.8552074513124471</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0104539793042737</v>
+        <v>0.009774808562368271</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8357290139296187</v>
+        <v>0.8362477357455836</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8783698388721047</v>
+        <v>0.8746781115879828</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.8229766014576141</v>
+        <v>0.8468718967229394</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.003382636065148403</v>
+        <v>0.003514771831338323</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.8170164105235739</v>
+        <v>0.8401645567372327</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.8293890730040615</v>
+        <v>0.8538886223865521</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.616600790513834</v>
+        <v>0.6819716407832546</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.01091541180304896</v>
+        <v>0.009761007213328302</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.5964583403919246</v>
+        <v>0.6632478632478632</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6372788886460762</v>
+        <v>0.7012468707115749</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1215904813632756</v>
+        <v>0.1122090732378589</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0018802766755469</v>
+        <v>0.002070285242805686</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.1178066547485856</v>
+        <v>0.108273141202185</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1253769734847732</v>
+        <v>0.1163626765606052</v>
       </c>
     </row>
     <row r="3">
@@ -769,124 +769,124 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8048793889148071</v>
+        <v>0.8688783077290223</v>
       </c>
       <c r="C3" t="n">
-        <v>0.005457426750857166</v>
+        <v>0.005046489695604556</v>
       </c>
       <c r="D3" t="n">
-        <v>0.794387207255339</v>
+        <v>0.8589962000244343</v>
       </c>
       <c r="E3" t="n">
-        <v>0.816145347957616</v>
+        <v>0.8784151639471383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7442084942084942</v>
+        <v>0.8217503217503217</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003692547606272704</v>
+        <v>0.004263762099438568</v>
       </c>
       <c r="H3" t="n">
-        <v>0.737367277992278</v>
+        <v>0.8132239382239382</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7512870012870013</v>
+        <v>0.8297981016731016</v>
       </c>
       <c r="J3" t="n">
-        <v>0.648062015503876</v>
+        <v>0.7724696356275303</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01756835559332687</v>
+        <v>0.01110739919710399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6163483650892275</v>
+        <v>0.750392464678179</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6818229739640631</v>
+        <v>0.7944333220016733</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2346996069623807</v>
+        <v>0.5356541268950028</v>
       </c>
       <c r="O3" t="n">
-        <v>0.009944195874573573</v>
+        <v>0.01164157505314511</v>
       </c>
       <c r="P3" t="n">
-        <v>0.215314430095452</v>
+        <v>0.513180797304885</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2540847838293094</v>
+        <v>0.5581134194272881</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2346996069623807</v>
+        <v>0.5356541268950028</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009944195874573573</v>
+        <v>0.01164157505314511</v>
       </c>
       <c r="T3" t="n">
-        <v>0.215314430095452</v>
+        <v>0.513180797304885</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2540847838293094</v>
+        <v>0.5581134194272881</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9488162344983089</v>
+        <v>0.936640360766629</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0032596527716564</v>
+        <v>0.003771999783338893</v>
       </c>
       <c r="X3" t="n">
-        <v>0.942728297632469</v>
+        <v>0.9289684329199549</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9553551296505073</v>
+        <v>0.9438556933483653</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.648062015503876</v>
+        <v>0.7724696356275303</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.01756835559332687</v>
+        <v>0.01110739919710399</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6163483650892275</v>
+        <v>0.750392464678179</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.6818229739640631</v>
+        <v>0.7944333220016733</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.755340154370849</v>
+        <v>0.8339690825135515</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.002488565043978918</v>
+        <v>0.003510068541655917</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.7503674682742806</v>
+        <v>0.8271912726126668</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.7601296752886557</v>
+        <v>0.8408682129800329</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.3446001648804617</v>
+        <v>0.6326259946949602</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.01227907748337074</v>
+        <v>0.01000180644252423</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.3190874434683778</v>
+        <v>0.6126706071842828</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.367442138406251</v>
+        <v>0.6519463781658903</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.1624325497282126</v>
+        <v>0.1286950088827094</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.001660132940605066</v>
+        <v>0.002274517307436558</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.1591146454520547</v>
+        <v>0.124353758075757</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1656827770433942</v>
+        <v>0.1332725833875725</v>
       </c>
     </row>
     <row r="4">
@@ -896,124 +896,124 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8863947201672167</v>
+        <v>0.8940310695320201</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004236589607891849</v>
+        <v>0.004300050899275022</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8781427769763134</v>
+        <v>0.8854185290429417</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8952582961069082</v>
+        <v>0.9021727957071608</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8309202059202059</v>
+        <v>0.8431467181467182</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003885753513838489</v>
+        <v>0.003878192480382096</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8235119047619047</v>
+        <v>0.8354247104247104</v>
       </c>
       <c r="I4" t="n">
-        <v>0.837998712998713</v>
+        <v>0.8508687258687259</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8529980657640233</v>
+        <v>0.856637168141593</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01068533170123762</v>
+        <v>0.009884700596450559</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8335758927526279</v>
+        <v>0.8370039226739046</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8743820060916369</v>
+        <v>0.8757897424357821</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4952274003368894</v>
+        <v>0.5435148792813026</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01180922444051812</v>
+        <v>0.01155107927975213</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4727400336889388</v>
+        <v>0.5199326221224031</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5174199887703537</v>
+        <v>0.5648512071869736</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4952274003368894</v>
+        <v>0.5435148792813026</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01180922444051812</v>
+        <v>0.01155107927975213</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4727400336889388</v>
+        <v>0.5199326221224031</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5174199887703537</v>
+        <v>0.5648512071869736</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9657271702367531</v>
+        <v>0.9634723788049605</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002819100140983828</v>
+        <v>0.002834596215395729</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9605411499436303</v>
+        <v>0.9578354002254792</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.9714825253664036</v>
+        <v>0.9688838782412627</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8529980657640233</v>
+        <v>0.856637168141593</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.01068533170123762</v>
+        <v>0.009884700596450559</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8335758927526279</v>
+        <v>0.8370039226739046</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8743820060916369</v>
+        <v>0.8757897424357821</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.8265148591277499</v>
+        <v>0.8401494298073142</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.003368885538692614</v>
+        <v>0.003420030090209169</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.8204080878551063</v>
+        <v>0.8333009113713559</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.8329642852269704</v>
+        <v>0.8465968833099845</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.6266429840142096</v>
+        <v>0.6650635520439712</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.01055471240712383</v>
+        <v>0.009868269431009885</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.6056682342275</v>
+        <v>0.6452271015030352</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6459486096444913</v>
+        <v>0.6836047668080953</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1245322689059638</v>
+        <v>0.1174971029832074</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001814343863270241</v>
+        <v>0.00194448514068042</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.1209816482058737</v>
+        <v>0.1137311172729792</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1278677766897534</v>
+        <v>0.1212715442741469</v>
       </c>
     </row>
     <row r="5">
@@ -1023,124 +1023,124 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8621245047466463</v>
+        <v>0.8775876137128287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005087317213119611</v>
+        <v>0.004842541772259066</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8523273315284029</v>
+        <v>0.8679789279549194</v>
       </c>
       <c r="E5" t="n">
-        <v>0.871846822624129</v>
+        <v>0.8869768007155576</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8172458172458172</v>
+        <v>0.8378378378378378</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004271613165217777</v>
+        <v>0.00405263574765952</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8090411840411841</v>
+        <v>0.8297940797940798</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8251287001287001</v>
+        <v>0.8457207207207207</v>
       </c>
       <c r="J5" t="n">
-        <v>0.77307366638442</v>
+        <v>0.813463098134631</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01154733714641084</v>
+        <v>0.01038220522646633</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7519620008313476</v>
+        <v>0.7927307597280018</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7965742269175745</v>
+        <v>0.8338766313971537</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5126333520494104</v>
+        <v>0.5631667602470523</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01153808975977464</v>
+        <v>0.01146114182840138</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4896125772038181</v>
+        <v>0.5412689500280741</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5339696799550814</v>
+        <v>0.5856260527793374</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5126333520494104</v>
+        <v>0.5631667602470523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01153808975977464</v>
+        <v>0.01146114182840138</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4896125772038181</v>
+        <v>0.5412689500280741</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5339696799550814</v>
+        <v>0.5856260527793374</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9395715896279594</v>
+        <v>0.9481397970687712</v>
       </c>
       <c r="W5" t="n">
-        <v>0.003700992624516002</v>
+        <v>0.003404878576913496</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9324633596392333</v>
+        <v>0.9411499436302142</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9470124013528749</v>
+        <v>0.9546786922209696</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.77307366638442</v>
+        <v>0.813463098134631</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.01154733714641084</v>
+        <v>0.01038220522646633</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.7519620008313476</v>
+        <v>0.7927307597280018</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7965742269175745</v>
+        <v>0.8338766313971537</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.8276067527308838</v>
+        <v>0.8438691551274333</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.003433200572368199</v>
+        <v>0.003481806870655062</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.8206077533851258</v>
+        <v>0.8373290858838354</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.8340878822848424</v>
+        <v>0.8505751749100313</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.6164753544902093</v>
+        <v>0.6655607166556071</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.01026272189224589</v>
+        <v>0.0095835445807603</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.5959731263542606</v>
+        <v>0.646174406949549</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6358640099723424</v>
+        <v>0.6836373747286406</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1283063720669532</v>
+        <v>0.1187965711981671</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.002364986634010082</v>
+        <v>0.002391082443506311</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.1238498140724548</v>
+        <v>0.1140709087101717</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.1327424247736357</v>
+        <v>0.1235003658006115</v>
       </c>
     </row>
     <row r="6">
@@ -1150,124 +1150,124 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.806780199614242</v>
+        <v>0.8688783077290223</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005392898869882041</v>
+        <v>0.005046489695604556</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7962987870842609</v>
+        <v>0.8589962000244343</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8179927133901821</v>
+        <v>0.8784151639471383</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7445302445302445</v>
+        <v>0.8217503217503217</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003626598457124782</v>
+        <v>0.004263762099438568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7378499034749034</v>
+        <v>0.8132239382239382</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7520149613899614</v>
+        <v>0.8297981016731016</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6548956661316212</v>
+        <v>0.7724696356275303</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01770496431089976</v>
+        <v>0.01110739919710399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6207675094221105</v>
+        <v>0.750392464678179</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6899655667293039</v>
+        <v>0.7944333220016733</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2290847838293094</v>
+        <v>0.5356541268950028</v>
       </c>
       <c r="O6" t="n">
-        <v>0.009762449986376476</v>
+        <v>0.01164157505314511</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2105277933745087</v>
+        <v>0.513180797304885</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2482032565974172</v>
+        <v>0.5581134194272881</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2290847838293094</v>
+        <v>0.5356541268950028</v>
       </c>
       <c r="S6" t="n">
-        <v>0.009762449986376476</v>
+        <v>0.01164157505314511</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2105277933745087</v>
+        <v>0.513180797304885</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2482032565974172</v>
+        <v>0.5581134194272881</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9515219842164599</v>
+        <v>0.936640360766629</v>
       </c>
       <c r="W6" t="n">
-        <v>0.003136053957597038</v>
+        <v>0.003771999783338893</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9455411499436303</v>
+        <v>0.9289684329199549</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9572773393461105</v>
+        <v>0.9438556933483653</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6548956661316212</v>
+        <v>0.7724696356275303</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.01770496431089976</v>
+        <v>0.01110739919710399</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6207675094221105</v>
+        <v>0.750392464678179</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.6899655667293039</v>
+        <v>0.7944333220016733</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.7545145717861613</v>
+        <v>0.8339690825135515</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.002439425316882911</v>
+        <v>0.003510068541655917</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.7498837054758107</v>
+        <v>0.8271912726126668</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.7591045977187529</v>
+        <v>0.8408682129800329</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.3394342762063228</v>
+        <v>0.6326259946949602</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.01221456725235256</v>
+        <v>0.01000180644252423</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.3156581921423059</v>
+        <v>0.6126706071842828</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.361825013192224</v>
+        <v>0.6519463781658903</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.1625354297474782</v>
+        <v>0.1286950088827094</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.001641965590736829</v>
+        <v>0.002274517307436558</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.1590582158239649</v>
+        <v>0.124353758075757</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.1659337481853095</v>
+        <v>0.1332725833875725</v>
       </c>
     </row>
     <row r="7">
@@ -1277,124 +1277,124 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.805538101987217</v>
+        <v>0.8674608655689805</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005410035409371594</v>
+        <v>0.00511077665524991</v>
       </c>
       <c r="D7" t="n">
-        <v>0.795260598690803</v>
+        <v>0.8574825684112709</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8170717700365945</v>
+        <v>0.8771024838154464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7446911196911197</v>
+        <v>0.8211068211068211</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003611011422587579</v>
+        <v>0.004237831321400232</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.8127413127413128</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7520149613899614</v>
+        <v>0.8293114543114544</v>
       </c>
       <c r="J7" t="n">
-        <v>0.656957928802589</v>
+        <v>0.7762180016515277</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01777323879696207</v>
+        <v>0.01119444485438726</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6231884057971014</v>
+        <v>0.7538966365873667</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6917397128940859</v>
+        <v>0.7985105001982375</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2279618192026951</v>
+        <v>0.527793374508703</v>
       </c>
       <c r="O7" t="n">
-        <v>0.009780797640266105</v>
+        <v>0.01165619238484596</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2088714205502527</v>
+        <v>0.5047725996631106</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2470522178551376</v>
+        <v>0.5502526670409882</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2279618192026951</v>
+        <v>0.527793374508703</v>
       </c>
       <c r="S7" t="n">
-        <v>0.009780797640266105</v>
+        <v>0.01165619238484596</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2088714205502527</v>
+        <v>0.5047725996631106</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2470522178551376</v>
+        <v>0.5502526670409882</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9521984216459978</v>
+        <v>0.9388951521984217</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003129842288878185</v>
+        <v>0.003714813944225496</v>
       </c>
       <c r="X7" t="n">
-        <v>0.946217587373168</v>
+        <v>0.9312232243517474</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9584047350620067</v>
+        <v>0.9463359639233371</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.656957928802589</v>
+        <v>0.7762180016515277</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01777323879696207</v>
+        <v>0.01119444485438726</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6231884057971014</v>
+        <v>0.7538966365873667</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.6917397128940859</v>
+        <v>0.7985105001982375</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.7543765630582351</v>
+        <v>0.8319680319680319</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002434744504673052</v>
+        <v>0.00348833422708985</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.7497549787532946</v>
+        <v>0.8251374447679923</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.7591328836441438</v>
+        <v>0.8387947693908898</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.338474364318466</v>
+        <v>0.6283422459893048</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.01225290388604163</v>
+        <v>0.0100879631854104</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.3144295779188217</v>
+        <v>0.6082509376065462</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.3626279552074173</v>
+        <v>0.648169146323848</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.162966909225989</v>
+        <v>0.1295322668027963</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.001633036122903157</v>
+        <v>0.002237356400745</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.1594993987370411</v>
+        <v>0.1252802331187337</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.1662843445646214</v>
+        <v>0.1340203198651545</v>
       </c>
     </row>
     <row r="8">
@@ -1404,124 +1404,124 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8054975891709242</v>
+        <v>0.8681407212673927</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005410430881047167</v>
+        <v>0.005093133120645564</v>
       </c>
       <c r="D8" t="n">
-        <v>0.795227781727074</v>
+        <v>0.8581153659415083</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8170440662333905</v>
+        <v>0.8778143493863257</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7445302445302445</v>
+        <v>0.8211068211068211</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003584200174299616</v>
+        <v>0.004256012639300714</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7377734877734877</v>
+        <v>0.8125804375804376</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7513714607464608</v>
+        <v>0.8291505791505791</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6564019448946515</v>
+        <v>0.773955773955774</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0177184505863198</v>
+        <v>0.01118146931845784</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6228528588564575</v>
+        <v>0.7519971500419111</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6907337519571397</v>
+        <v>0.7957191207185348</v>
       </c>
       <c r="N8" t="n">
-        <v>0.227400336889388</v>
+        <v>0.5306007860752386</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00970291075820669</v>
+        <v>0.01161911676595873</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2077484559236384</v>
+        <v>0.5075800112296462</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2453677709152162</v>
+        <v>0.5530741156653565</v>
       </c>
       <c r="R8" t="n">
-        <v>0.227400336889388</v>
+        <v>0.5306007860752386</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00970291075820669</v>
+        <v>0.01161911676595873</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2077484559236384</v>
+        <v>0.5075800112296462</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2453677709152162</v>
+        <v>0.5530741156653565</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9521984216459978</v>
+        <v>0.9377677564825254</v>
       </c>
       <c r="W8" t="n">
-        <v>0.003129842288878185</v>
+        <v>0.003742220741836255</v>
       </c>
       <c r="X8" t="n">
-        <v>0.946217587373168</v>
+        <v>0.9301014656144306</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9584047350620067</v>
+        <v>0.944988726042841</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.6564019448946515</v>
+        <v>0.773955773955774</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0177184505863198</v>
+        <v>0.01118146931845784</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6228528588564575</v>
+        <v>0.7519971500419111</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.6907337519571397</v>
+        <v>0.7957191207185348</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.7542418288980175</v>
+        <v>0.8326326326326327</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.002412672078846074</v>
+        <v>0.003491144750521542</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.7495534949688687</v>
+        <v>0.8258431985651723</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.7590154310326411</v>
+        <v>0.8394271891597429</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.3377814845704754</v>
+        <v>0.6295802798134577</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0121577780152179</v>
+        <v>0.01005177392917158</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.3138819756868</v>
+        <v>0.6092404630904019</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.3613227881905551</v>
+        <v>0.6488809023770614</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.1629904621569982</v>
+        <v>0.1290992267780757</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.001631637167774613</v>
+        <v>0.002250617661862305</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.159519157941783</v>
+        <v>0.1247938547589988</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.1663005764723914</v>
+        <v>0.1336085235248442</v>
       </c>
     </row>
     <row r="9">
@@ -1531,124 +1531,124 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.805520251027538</v>
+        <v>0.8678188975829675</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005410099519262004</v>
+        <v>0.005101287860030215</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7952523726900573</v>
+        <v>0.857810304434824</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8170601447573568</v>
+        <v>0.8774696327956313</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7448519948519948</v>
+        <v>0.8212676962676962</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003596381321928977</v>
+        <v>0.004250688721712639</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7380952380952381</v>
+        <v>0.8129021879021879</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7520149613899614</v>
+        <v>0.8294723294723295</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6575121163166397</v>
+        <v>0.7754934210526315</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01769655967585781</v>
+        <v>0.01120161960456549</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6234674899568516</v>
+        <v>0.753472450008974</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6922595891345891</v>
+        <v>0.7974771153682779</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2285233015160023</v>
+        <v>0.5294778214486243</v>
       </c>
       <c r="O9" t="n">
-        <v>0.009750312495697718</v>
+        <v>0.01163645456775406</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2088714205502527</v>
+        <v>0.5058955642897248</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2473469960696238</v>
+        <v>0.5519371139809096</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2285233015160023</v>
+        <v>0.5294778214486243</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009750312495697718</v>
+        <v>0.01163645456775406</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2088714205502527</v>
+        <v>0.5058955642897248</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2473469960696238</v>
+        <v>0.5519371139809096</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9521984216459978</v>
+        <v>0.9384441939120631</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003129842288878185</v>
+        <v>0.003730162437699184</v>
       </c>
       <c r="X9" t="n">
-        <v>0.946217587373168</v>
+        <v>0.9307779030439685</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9584047350620067</v>
+        <v>0.9458850056369785</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6575121163166397</v>
+        <v>0.7754934210526315</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01769655967585781</v>
+        <v>0.01120161960456549</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6234674899568516</v>
+        <v>0.753472450008974</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.6922595891345891</v>
+        <v>0.7974771153682779</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.7545113453635877</v>
+        <v>0.8324</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.002425707799653222</v>
+        <v>0.003490628196494364</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.7498880241484597</v>
+        <v>0.8255323606670742</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.7593809717496646</v>
+        <v>0.8391503521777356</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.3391666666666667</v>
+        <v>0.629295962629296</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.01219848808720566</v>
+        <v>0.01007312917251269</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.3150430449822065</v>
+        <v>0.6088897533809376</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.3631500279581917</v>
+        <v>0.6488457650112837</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.1629782164875765</v>
+        <v>0.1293162885286447</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.001632338757603133</v>
+        <v>0.002243806696853376</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.1595089424483838</v>
+        <v>0.1250385734110964</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.166292012388664</v>
+        <v>0.1337988574026568</v>
       </c>
     </row>
   </sheetData>
